--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -865,7 +865,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -888,7 +888,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -941,26 +941,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -972,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1288,15 +1270,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1341,7 +1323,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -1362,7 +1344,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -1372,7 +1354,7 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="3"/>
@@ -1383,7 +1365,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1393,7 +1375,9 @@
       <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
@@ -1402,7 +1386,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -1421,7 +1405,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -1440,7 +1424,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1459,7 +1443,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1478,7 +1462,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -1497,7 +1481,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
         <v>36</v>
       </c>
@@ -1516,7 +1500,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
@@ -1548,7 +1532,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
         <v>43</v>
       </c>
@@ -1567,7 +1551,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
         <v>47</v>
       </c>
@@ -1586,7 +1570,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
         <v>50</v>
       </c>
@@ -1605,7 +1589,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
         <v>53</v>
       </c>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1365,7 +1365,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1396,7 +1396,9 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
@@ -1608,7 +1610,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
         <v>56</v>
       </c>
@@ -1640,7 +1642,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
@@ -1659,7 +1661,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
         <v>64</v>
       </c>
@@ -1678,7 +1680,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
         <v>67</v>
       </c>
@@ -1697,7 +1699,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
         <v>70</v>
       </c>
@@ -1716,7 +1718,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
         <v>73</v>
       </c>
@@ -1735,7 +1737,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
         <v>76</v>
       </c>
@@ -1754,7 +1756,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -1773,7 +1775,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
         <v>82</v>
       </c>
@@ -1786,7 +1788,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
         <v>83</v>
       </c>
@@ -1805,7 +1807,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
         <v>87</v>
       </c>
@@ -1824,7 +1826,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -1837,7 +1839,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
         <v>91</v>
       </c>
@@ -1856,7 +1858,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
         <v>95</v>
       </c>
@@ -1875,7 +1877,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
         <v>98</v>
       </c>
@@ -1894,7 +1896,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
         <v>101</v>
       </c>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1417,7 +1417,9 @@
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
@@ -2385,7 +2387,7 @@
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
         <v>177</v>
       </c>
@@ -2398,7 +2400,7 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
         <v>178</v>
       </c>
@@ -2417,7 +2419,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
         <v>182</v>
       </c>
@@ -2436,7 +2438,7 @@
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
         <v>185</v>
       </c>
@@ -2455,7 +2457,7 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
         <v>188</v>
       </c>
@@ -2468,7 +2470,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
         <v>189</v>
       </c>
@@ -2487,7 +2489,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
         <v>193</v>
       </c>
@@ -2506,7 +2508,7 @@
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
         <v>195</v>
       </c>
@@ -2525,7 +2527,7 @@
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
         <v>198</v>
       </c>
@@ -2538,7 +2540,7 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
         <v>199</v>
       </c>
@@ -2557,7 +2559,7 @@
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
         <v>203</v>
       </c>
@@ -2576,7 +2578,7 @@
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
         <v>206</v>
       </c>
@@ -2595,7 +2597,7 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
         <v>209</v>
       </c>
@@ -2614,7 +2616,7 @@
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
         <v>212</v>
       </c>
@@ -2633,7 +2635,7 @@
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
         <v>215</v>
       </c>
@@ -2646,7 +2648,7 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
         <v>216</v>
       </c>
@@ -2665,7 +2667,7 @@
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
         <v>220</v>
       </c>
@@ -2684,7 +2686,7 @@
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
         <v>223</v>
       </c>
@@ -2703,7 +2705,7 @@
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
         <v>226</v>
       </c>
@@ -2722,7 +2724,7 @@
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
         <v>229</v>
       </c>
@@ -2735,7 +2737,7 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
         <v>230</v>
       </c>
@@ -2754,7 +2756,7 @@
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
         <v>234</v>
       </c>
@@ -2773,7 +2775,7 @@
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
         <v>237</v>
       </c>
@@ -2792,7 +2794,7 @@
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
         <v>240</v>
       </c>
@@ -2811,7 +2813,7 @@
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
         <v>243</v>
       </c>
@@ -2824,7 +2826,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
         <v>244</v>
       </c>
@@ -2843,7 +2845,7 @@
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
         <v>248</v>
       </c>
@@ -2862,7 +2864,7 @@
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
         <v>251</v>
       </c>
@@ -2875,7 +2877,7 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
         <v>252</v>
       </c>
@@ -2894,7 +2896,7 @@
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
         <v>256</v>
       </c>
@@ -2913,7 +2915,7 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
         <v>259</v>
       </c>
@@ -2932,7 +2934,7 @@
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
         <v>262</v>
       </c>
@@ -2951,7 +2953,7 @@
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
         <v>265</v>
       </c>
@@ -2970,7 +2972,7 @@
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
         <v>268</v>
       </c>
@@ -2989,7 +2991,7 @@
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
         <v>271</v>
       </c>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1386,7 +1386,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -1407,7 +1407,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -1438,7 +1438,9 @@
       <c r="C8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1428,7 +1428,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -1459,7 +1459,9 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1449,7 +1449,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1480,7 +1480,9 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="275">
   <si>
     <t>Command</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Move or rename files</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -945,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,6 +960,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1270,15 +1276,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1480,58 +1486,58 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>13</v>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1544,102 +1550,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1652,140 +1658,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1798,45 +1804,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1849,83 +1855,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1938,121 +1944,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2065,140 +2071,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2211,102 +2217,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2319,83 +2325,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2408,64 +2414,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2478,64 +2484,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2548,102 +2554,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2656,83 +2662,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2745,83 +2751,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2834,45 +2840,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2885,133 +2891,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>Move or rename files</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -948,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -960,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1276,15 +1270,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1486,58 +1480,58 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>35</v>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1550,102 +1544,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1658,140 +1652,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1804,45 +1798,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1855,83 +1849,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1944,121 +1938,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2071,140 +2065,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2217,102 +2211,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2325,83 +2319,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2414,64 +2408,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2484,64 +2478,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2554,102 +2548,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2662,83 +2656,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2751,83 +2745,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2840,45 +2834,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2891,133 +2885,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -112,6 +112,9 @@
     <t>Copy files and directories</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
   </si>
   <si>
     <t>Move or rename files</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -1465,29 +1465,29 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -112,16 +112,16 @@
     <t>Copy files and directories</t>
   </si>
   <si>
+    <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
+  </si>
+  <si>
+    <t>mv</t>
+  </si>
+  <si>
+    <t>Move or rename files</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
-  </si>
-  <si>
-    <t>mv</t>
-  </si>
-  <si>
-    <t>Move or rename files</t>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -1465,29 +1465,29 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Copy files and directories</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -948,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -960,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1276,15 +1270,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1455,7 +1449,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -1465,79 +1459,77 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1550,102 +1542,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1658,140 +1650,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1804,45 +1796,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1855,83 +1847,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1944,121 +1936,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2071,140 +2063,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2217,102 +2209,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2325,83 +2317,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2414,64 +2406,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2484,64 +2476,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2554,102 +2546,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2662,83 +2654,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2751,83 +2743,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2840,45 +2832,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2891,133 +2883,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="275">
   <si>
     <t>Command</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>Copy files and directories</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -945,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,6 +960,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1270,15 +1276,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1459,77 +1465,77 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1542,102 +1548,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1650,140 +1656,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1796,45 +1802,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1847,83 +1853,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1936,121 +1942,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2063,140 +2069,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2209,102 +2215,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2317,83 +2323,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2406,64 +2412,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2476,64 +2482,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2546,102 +2552,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2654,83 +2660,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2743,83 +2749,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2832,45 +2838,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2883,133 +2889,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Copy files and directories</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -948,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -960,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1276,15 +1270,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1465,77 +1459,77 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1548,102 +1542,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1656,140 +1650,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1802,45 +1796,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1853,83 +1847,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1942,121 +1936,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2069,140 +2063,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2215,102 +2209,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2323,83 +2317,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2412,64 +2406,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2482,64 +2476,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2552,102 +2546,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2660,83 +2654,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2749,83 +2743,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2838,45 +2832,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2889,133 +2883,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1480,7 +1480,9 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1501,7 +1501,9 @@
       <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -1522,7 +1522,9 @@
       <c r="C12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="273">
   <si>
     <t>Command</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Powerful search with many filter options</t>
-  </si>
-  <si>
-    <t>FILE CONTENT VIEWING</t>
   </si>
   <si>
     <t>cat</t>
@@ -1534,116 +1531,116 @@
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1656,140 +1653,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1802,45 +1799,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1853,83 +1850,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1942,121 +1939,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2069,140 +2066,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2215,102 +2212,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2323,83 +2320,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2412,64 +2409,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2482,64 +2479,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2552,102 +2549,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>210</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2660,83 +2657,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2749,83 +2746,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>240</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>241</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2838,45 +2835,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2889,133 +2886,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Powerful search with many filter options</t>
+  </si>
+  <si>
+    <t>FILE CONTENT VIEWING</t>
   </si>
   <si>
     <t>cat</t>
@@ -1531,116 +1534,116 @@
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1653,140 +1656,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1799,45 +1802,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1850,83 +1853,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1939,121 +1942,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2066,140 +2069,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2212,102 +2215,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2320,83 +2323,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2409,64 +2412,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2479,64 +2482,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2549,102 +2552,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2657,83 +2660,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2746,83 +2749,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2835,45 +2838,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2886,133 +2889,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="275">
   <si>
     <t>Command</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Search for files</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Powerful search with many filter options</t>
@@ -945,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,6 +960,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1270,15 +1276,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1522,20 +1528,20 @@
       <c r="C12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>13</v>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1548,102 +1554,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1656,140 +1662,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1802,45 +1808,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1853,83 +1859,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1942,121 +1948,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2069,140 +2075,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2215,102 +2221,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2323,83 +2329,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2412,64 +2418,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2482,64 +2488,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2552,102 +2558,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2660,83 +2666,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2749,83 +2755,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2838,45 +2844,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2889,133 +2895,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -130,6 +130,9 @@
     <t>Create empty file</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Updates timestamp if file exists</t>
   </si>
   <si>
@@ -137,9 +140,6 @@
   </si>
   <si>
     <t>Search for files</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Powerful search with many filter options</t>
@@ -1507,29 +1507,29 @@
       <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>13</v>
+      <c r="D11" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -121,6 +121,9 @@
     <t>Move or rename files</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Works for both moving and renaming</t>
   </si>
   <si>
@@ -128,9 +131,6 @@
   </si>
   <si>
     <t>Create empty file</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Updates timestamp if file exists</t>
@@ -1486,29 +1486,29 @@
       <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>13</v>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1529,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -112,6 +112,9 @@
     <t>Copy files and directories</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
   </si>
   <si>
     <t>Move or rename files</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -1465,29 +1465,29 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1508,7 +1508,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1529,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -112,16 +112,16 @@
     <t>Copy files and directories</t>
   </si>
   <si>
+    <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
+  </si>
+  <si>
+    <t>mv</t>
+  </si>
+  <si>
+    <t>Move or rename files</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
-  </si>
-  <si>
-    <t>mv</t>
-  </si>
-  <si>
-    <t>Move or rename files</t>
   </si>
   <si>
     <t>Works for both moving and renaming</t>
@@ -1465,29 +1465,29 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1508,7 +1508,7 @@
         <v>38</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1529,7 +1529,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
   <si>
     <t>Command</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>Copy files and directories</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -948,7 +945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -960,9 +957,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1276,15 +1270,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1465,83 +1459,77 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
+      <c r="D9" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1554,102 +1542,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1662,140 +1650,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1808,45 +1796,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1859,83 +1847,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1948,121 +1936,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2075,140 +2063,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2221,102 +2209,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2329,83 +2317,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2418,64 +2406,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2488,64 +2476,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2558,102 +2546,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2666,83 +2654,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2755,83 +2743,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2844,45 +2832,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2895,133 +2883,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="275">
   <si>
     <t>Command</t>
   </si>
@@ -110,6 +110,10 @@
   </si>
   <si>
     <t>Copy files and directories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✅&amp;#10;
+</t>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -1460,76 +1464,76 @@
         <v>31</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1542,102 +1546,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -1650,140 +1654,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1796,45 +1800,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1847,83 +1851,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1936,121 +1940,121 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
       <c r="A37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
       <c r="A39" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
       <c r="A40" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
       <c r="A41" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
       <c r="A42" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2063,140 +2067,140 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
       <c r="A43" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
       <c r="A44" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
       <c r="A45" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
       <c r="A46" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
       <c r="A48" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
       <c r="A49" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2209,102 +2213,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
       <c r="A51" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
       <c r="A52" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
       <c r="A53" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
       <c r="A54" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
       <c r="A55" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2317,83 +2321,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
       <c r="A57" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
       <c r="A58" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
       <c r="A59" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
       <c r="A60" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2406,64 +2410,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2476,64 +2480,64 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2546,102 +2550,102 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2654,83 +2658,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -2743,83 +2747,83 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -2832,45 +2836,45 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -2883,133 +2887,133 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="19.5">
       <c r="A95" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>

--- a/linux_command_practice_tracker.xlsx
+++ b/linux_command_practice_tracker.xlsx
@@ -112,8 +112,7 @@
     <t>Copy files and directories</t>
   </si>
   <si>
-    <t xml:space="preserve">✅&amp;#10;
-</t>
+    <t/>
   </si>
   <si>
     <t>Use &amp;apos;-r&amp;apos; for recursive copy of folders</t>
@@ -949,7 +948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -961,6 +960,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1274,15 +1276,15 @@
   <dimension ref="A1:I95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="5" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="25.005" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="30.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="6" width="25.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
@@ -1463,7 +1465,7 @@
       <c r="C9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="3"/>
